--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -631,6 +631,55 @@
         <v>0.5600000000000001</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>41.333</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>60.143</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -642,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -742,6 +791,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -753,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -853,6 +933,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -864,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1036,6 +1147,55 @@
         <v>0.5600000000000001</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>41.333</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>60.143</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1047,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1147,6 +1307,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -680,6 +680,55 @@
         <v>0.55</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>60.857</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>9.163</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -691,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -822,6 +871,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -833,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -964,6 +1044,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -975,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1196,6 +1307,55 @@
         <v>0.55</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>60.857</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>9.163</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1207,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1338,6 +1498,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -729,6 +729,55 @@
         <v>0.83</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>60.857</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>9.163</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -740,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -902,6 +951,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -913,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1075,6 +1155,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1086,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1356,6 +1467,55 @@
         <v>0.83</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>60.857</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>9.163</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1367,7 +1527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1529,6 +1689,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -778,6 +778,55 @@
         <v>0.83</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>60.857</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>9.163</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -789,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -982,6 +1031,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -993,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1186,6 +1266,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1197,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1516,6 +1627,55 @@
         <v>0.83</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>60.857</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>9.163</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1527,7 +1687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1720,6 +1880,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -827,6 +827,55 @@
         <v>0.83</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>41.667</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>61.095</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>9.163</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -838,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1062,6 +1111,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1073,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1297,6 +1377,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1308,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1676,6 +1787,55 @@
         <v>0.83</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>41.667</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>61.095</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>9.163</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1687,7 +1847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1911,6 +2071,37 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -876,6 +876,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>41.667</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>61.143</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>9.212999999999999</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -887,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1142,6 +1191,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1153,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1408,6 +1488,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1419,7 +1530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1836,6 +1947,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>41.667</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>61.143</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>4.864</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>9.212999999999999</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1847,7 +2007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2102,6 +2262,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -925,6 +925,55 @@
         <v>0.55</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>41.667</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>61.333</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>4.854</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>9.212999999999999</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -936,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1222,6 +1271,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1233,7 +1313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1519,6 +1599,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1530,7 +1641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2107,55 @@
         <v>0.55</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>41.667</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>61.333</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>4.854</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>9.212999999999999</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2007,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2293,6 +2453,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -974,6 +974,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>41.833</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>61.595</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>12.325</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>4.854</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>9.275</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -985,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1302,6 +1351,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1313,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1630,6 +1710,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1641,7 +1752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2267,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>41.833</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>61.595</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>12.325</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>4.854</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>9.275</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2167,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2484,6 +2644,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1023,6 +1023,55 @@
         <v>0.67</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>61.952</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1034,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1382,6 +1431,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1393,7 +1473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1741,6 +1821,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1752,7 +1863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2316,6 +2427,55 @@
         <v>0.67</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>61.952</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2327,7 +2487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2675,6 +2835,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1072,6 +1072,55 @@
         <v>1.35</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>61.952</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1083,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1462,6 +1511,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1473,7 +1553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1852,6 +1932,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1863,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2476,6 +2587,55 @@
         <v>1.35</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>61.952</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2487,7 +2647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2866,6 +3026,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1121,6 +1121,55 @@
         <v>1.35</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>61.952</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1132,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1542,6 +1591,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1553,7 +1633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1963,6 +2043,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1974,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2636,6 +2747,55 @@
         <v>1.35</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>61.952</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2647,7 +2807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3057,6 +3217,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>21.682</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1170,6 +1170,55 @@
         <v>1.35</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>41.933</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>62.625</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>4.882</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>9.475</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1181,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1622,6 +1671,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1633,7 +1713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2154,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2085,7 +2196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2796,6 +2907,55 @@
         <v>1.35</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>41.933</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>62.625</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>4.882</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>9.475</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2807,7 +2967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3248,6 +3408,37 @@
         <v>5.3</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1219,6 +1219,55 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>42.567</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>4.882</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1230,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1702,6 +1751,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1713,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2185,6 +2265,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2196,7 +2307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2956,6 +3067,55 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>42.567</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>4.882</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2967,7 +3127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3439,6 +3599,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1268,55 @@
         <v>0.79</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>42.833</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>4.871</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1279,7 +1328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1782,6 +1831,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1793,7 +1873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2296,6 +2376,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2307,7 +2418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3116,6 +3227,55 @@
         <v>0.79</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>42.833</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>4.871</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3127,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3630,6 +3790,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1317,6 +1317,55 @@
         <v>1.82</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>43.233</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>4.825</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1328,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1862,6 +1911,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1873,7 +1953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2407,6 +2487,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2418,7 +2529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3276,6 +3387,55 @@
         <v>1.82</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>43.233</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>4.825</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3287,7 +3447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3821,6 +3981,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1366,6 +1366,55 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>64.125</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4.793</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>10.025</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1377,7 +1426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1942,6 +1991,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1953,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2518,6 +2598,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2529,7 +2640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3436,6 +3547,55 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>64.125</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4.793</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>10.025</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3447,7 +3607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4012,6 +4172,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1415,6 +1415,55 @@
         <v>1.26</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>64.125</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>4.793</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>10.025</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1426,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2022,6 +2071,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2033,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2629,6 +2709,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2640,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3596,6 +3707,55 @@
         <v>1.26</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>64.125</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>4.793</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>10.025</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3607,7 +3767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4203,6 +4363,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1464,6 +1464,55 @@
         <v>1.26</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>64.125</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>4.793</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>10.025</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1475,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2102,6 +2151,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2113,7 +2193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2740,6 +2820,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2751,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3756,6 +3867,55 @@
         <v>1.26</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>64.125</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>4.793</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>10.025</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3767,7 +3927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4394,6 +4554,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>22.182</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1513,6 +1513,55 @@
         <v>1.26</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>43.467</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>64.375</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>10.167</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1524,7 +1573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2231,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2193,7 +2273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2851,6 +2931,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2862,7 +2973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3916,6 +4027,55 @@
         <v>1.26</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>43.467</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>64.375</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>10.167</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3927,7 +4087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4585,6 +4745,37 @@
         <v>2.07</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1562,6 +1562,55 @@
         <v>1.42</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>64.875</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>4.729</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>10.314</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1573,7 +1622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2262,6 +2311,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2273,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2962,6 +3042,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2973,7 +3084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4076,6 +4187,55 @@
         <v>1.42</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>64.875</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>4.729</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>10.314</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4087,7 +4247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4776,6 +4936,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1611,6 +1611,55 @@
         <v>1.45</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>4.707</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>10.433</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1622,7 +1671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2342,6 +2391,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2353,7 +2433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3073,6 +3153,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3084,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4236,6 +4347,55 @@
         <v>1.45</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>4.707</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>10.433</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4247,7 +4407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4967,6 +5127,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1660,6 +1660,55 @@
         <v>1.15</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>44.667</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>11.988</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>4.664</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>10.548</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1671,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2422,6 +2471,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2433,7 +2513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3184,6 +3264,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3195,7 +3306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4396,6 +4507,55 @@
         <v>1.15</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>44.667</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>11.988</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>4.664</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>10.548</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4407,7 +4567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5158,6 +5318,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1709,6 +1709,55 @@
         <v>1.1</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>44.833</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>4.643</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>10.671</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1720,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2502,6 +2551,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2513,7 +2593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3295,6 +3375,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3306,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4556,6 +4667,55 @@
         <v>1.1</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>44.833</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>4.643</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>10.671</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4567,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5349,6 +5509,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1758,6 +1758,55 @@
         <v>1.17</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>44.833</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>4.643</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>10.671</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1769,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2582,6 +2631,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2593,7 +2673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3406,6 +3486,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3417,7 +3528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4716,6 +4827,55 @@
         <v>1.17</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>44.833</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>4.643</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>10.671</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4727,7 +4887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5540,6 +5700,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1807,6 +1807,55 @@
         <v>1.17</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>44.833</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>4.643</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>10.671</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1818,7 +1867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2662,6 +2711,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2673,7 +2753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3517,6 +3597,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3528,7 +3639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4876,6 +4987,55 @@
         <v>1.17</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>44.833</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>4.643</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>10.671</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4887,7 +5047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5731,6 +5891,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>24.318</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>12.233</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>6.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1856,6 +1856,55 @@
         <v>1.17</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>10.743</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1867,7 +1916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2742,6 +2791,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2753,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3628,6 +3708,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3639,7 +3750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5036,6 +5147,55 @@
         <v>1.17</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>10.743</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5047,7 +5207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5922,6 +6082,37 @@
         <v>6.37</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1905,6 +1905,55 @@
         <v>0.68</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>45.233</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>68.125</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>4.519</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>10.857</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1916,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2822,6 +2871,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2833,7 +2913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3739,6 +3819,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3750,7 +3861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5196,6 +5307,55 @@
         <v>0.68</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>45.233</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>68.125</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>4.519</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>10.857</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5207,7 +5367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6113,6 +6273,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1954,6 +1954,55 @@
         <v>1.06</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>4.476</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>10.952</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1965,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2902,6 +2951,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2913,7 +2993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3850,6 +3930,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3861,7 +3972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5356,6 +5467,55 @@
         <v>1.06</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>4.476</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>10.952</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5367,7 +5527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6304,6 +6464,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2003,6 +2003,55 @@
         <v>0.88</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>10.976</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2014,7 +2063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2982,6 +3031,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2993,7 +3073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3961,6 +4041,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3972,7 +4083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5516,6 +5627,55 @@
         <v>0.88</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>10.976</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5527,7 +5687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6495,6 +6655,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2052,55 @@
         <v>0.22</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>10.976</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2063,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3062,6 +3111,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3073,7 +3153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4072,6 +4152,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4083,7 +4194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5676,6 +5787,55 @@
         <v>0.22</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>10.976</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5687,7 +5847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6686,6 +6846,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2101,6 +2101,55 @@
         <v>0.22</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>10.976</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2112,7 +2161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3142,6 +3191,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3153,7 +3233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4183,6 +4263,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4194,7 +4305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5836,6 +5947,55 @@
         <v>0.22</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>10.976</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5847,7 +6007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6877,6 +7037,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2150,6 +2150,55 @@
         <v>0.22</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>10.976</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2161,7 +2210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3222,6 +3271,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3233,7 +3313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4294,6 +4374,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4305,7 +4416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5996,6 +6107,55 @@
         <v>0.22</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>10.976</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6007,7 +6167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7068,6 +7228,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>26.545</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>13.267</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2199,6 +2199,55 @@
         <v>0.22</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>46.167</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>11.152</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2210,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3302,6 +3351,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3313,7 +3393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4405,6 +4485,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4416,7 +4527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6156,6 +6267,55 @@
         <v>0.22</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>46.167</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>11.152</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6167,7 +6327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7259,6 +7419,37 @@
         <v>8.449999999999999</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2248,55 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>70.634</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>11.271</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2259,7 +2308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3382,6 +3431,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3393,7 +3473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4516,6 +4596,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4527,7 +4638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6316,6 +6427,55 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>70.634</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>11.271</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6327,7 +6487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7450,6 +7610,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2297,6 +2297,55 @@
         <v>1.07</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>46.667</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>71.30500000000001</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>11.386</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2308,7 +2357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3462,6 +3511,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3473,7 +3553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4627,6 +4707,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4638,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6476,6 +6587,55 @@
         <v>1.07</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>46.667</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>71.30500000000001</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>11.386</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6487,7 +6647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7641,6 +7801,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2346,6 +2346,55 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>71.58499999999999</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>4.321</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2357,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3542,6 +3591,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3553,7 +3633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4738,6 +4818,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4749,7 +4860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6636,6 +6747,55 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>71.58499999999999</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>4.321</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6647,7 +6807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7832,6 +7992,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2395,6 +2395,55 @@
         <v>1</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>72.31699999999999</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>11.571</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2406,7 +2455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3622,6 +3671,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3633,7 +3713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4849,6 +4929,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4860,7 +4971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6796,6 +6907,55 @@
         <v>1</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>72.31699999999999</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>11.571</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6807,7 +6967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8023,6 +8183,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2444,6 +2444,55 @@
         <v>0.62</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>72.31699999999999</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>11.571</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2455,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3702,6 +3751,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3713,7 +3793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4960,6 +5040,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4971,7 +5082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6956,6 +7067,55 @@
         <v>0.62</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>72.31699999999999</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>11.571</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6967,7 +7127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8214,6 +8374,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2493,6 +2493,55 @@
         <v>0.62</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>72.31699999999999</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>11.571</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2504,7 +2553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3782,6 +3831,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3793,7 +3873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5071,6 +5151,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5082,7 +5193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7116,6 +7227,55 @@
         <v>0.62</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>72.31699999999999</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>11.571</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7127,7 +7287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8405,6 +8565,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>28.182</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2542,6 +2542,55 @@
         <v>0.62</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>72.988</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>4.279</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>11.762</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2553,7 +2602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3862,6 +3911,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3873,7 +3953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5182,6 +5262,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5193,7 +5304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7276,6 +7387,55 @@
         <v>0.62</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>46.733</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>72.988</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>4.279</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>11.762</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7287,7 +7447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8596,6 +8756,37 @@
         <v>5.53</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2591,6 +2591,55 @@
         <v>1.65</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>46.833</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>73.744</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>4.257</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>12.038</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2602,7 +2651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3942,6 +3991,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3953,7 +4033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5293,6 +5373,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5304,7 +5415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7436,6 +7547,55 @@
         <v>1.65</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>46.833</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>73.744</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>4.257</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>12.038</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7447,7 +7607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8787,6 +8947,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2640,6 +2640,55 @@
         <v>2.35</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>46.833</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>11.625</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>4.236</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>12.171</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2651,7 +2700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4022,6 +4071,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4033,7 +4113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5404,6 +5484,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5415,7 +5526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7596,6 +7707,55 @@
         <v>2.35</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>46.833</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>11.625</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>4.236</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>12.171</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7607,7 +7767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8978,6 +9138,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2689,6 +2689,55 @@
         <v>1.11</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>46.667</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>4.204</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>12.341</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2700,7 +2749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4102,6 +4151,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4113,7 +4193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5515,6 +5595,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5526,7 +5637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7756,6 +7867,55 @@
         <v>1.11</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>46.667</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>4.204</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>12.341</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7767,7 +7927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9169,6 +9329,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2738,6 +2738,55 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>46.633</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>12.476</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2749,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4182,6 +4231,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4193,7 +4273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5626,6 +5706,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5637,7 +5748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7916,6 +8027,55 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>46.633</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>12.476</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7927,7 +8087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9360,6 +9520,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2787,6 +2787,55 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>46.667</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>12.476</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2798,7 +2847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4262,6 +4311,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4273,7 +4353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5737,6 +5817,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5748,7 +5859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8076,6 +8187,55 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>46.667</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>12.476</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8087,7 +8247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9551,6 +9711,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2836,6 +2836,55 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>46.667</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>12.476</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2847,7 +2896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4342,6 +4391,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4353,7 +4433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5848,6 +5928,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5859,7 +5970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8236,6 +8347,55 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>46.667</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>76.375</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>12.476</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8247,7 +8407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9742,6 +9902,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>29.068</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2885,6 +2885,55 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>4.114</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>12.675</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2896,7 +2945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4422,6 +4471,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4433,7 +4513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5959,6 +6039,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5970,7 +6081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8396,6 +8507,55 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>4.114</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>12.675</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8407,7 +8567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9933,6 +10093,37 @@
         <v>3.57</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2934,6 +2934,55 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>47.233</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>77.175</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2945,7 +2994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4502,6 +4551,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4513,7 +4593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6070,6 +6150,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6081,7 +6192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8556,6 +8667,55 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>47.233</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>77.175</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8567,7 +8727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10124,6 +10284,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2983,6 +2983,55 @@
         <v>0.59</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>47.067</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>77.175</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>12.825</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2994,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4582,6 +4631,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4593,7 +4673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6181,6 +6261,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6192,7 +6303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8716,6 +8827,55 @@
         <v>0.59</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>47.067</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>77.175</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>12.825</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8727,7 +8887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10315,6 +10475,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3032,6 +3032,55 @@
         <v>0.59</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>47.767</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>77.125</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>12.875</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3043,7 +3092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4662,6 +4711,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4673,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6292,6 +6372,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6303,7 +6414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8876,6 +8987,55 @@
         <v>0.59</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>47.767</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>77.125</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>12.875</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8887,7 +9047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10506,6 +10666,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3081,6 +3081,55 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3092,7 +3141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4742,6 +4791,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4753,7 +4833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6403,6 +6483,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6414,7 +6525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9036,6 +9147,55 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9047,7 +9207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10697,6 +10857,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3130,6 +3130,55 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3141,7 +3190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4822,6 +4871,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4833,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6514,6 +6594,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6525,7 +6636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9196,6 +9307,55 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9207,7 +9367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10888,6 +11048,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3179,6 +3179,55 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3190,7 +3239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4902,6 +4951,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4913,7 +4993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6625,6 +6705,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6636,7 +6747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9356,6 +9467,55 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9367,7 +9527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11079,6 +11239,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>29.682</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>14.733</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3228,6 +3228,55 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>48.167</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3239,7 +3288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4982,6 +5031,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4993,7 +5073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6736,6 +6816,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6747,7 +6858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9516,6 +9627,55 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>48.167</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9527,7 +9687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11270,6 +11430,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3277,6 +3277,55 @@
         <v>0.19</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>78.375</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3288,7 +3337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5062,6 +5111,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5073,7 +5153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6847,6 +6927,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6858,7 +6969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9676,6 +9787,55 @@
         <v>0.19</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>78.375</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9687,7 +9847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11461,6 +11621,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3326,6 +3326,55 @@
         <v>0.77</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>48.567</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>78.625</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3337,7 +3386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5142,6 +5191,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5153,7 +5233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6958,6 +7038,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6969,7 +7080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9836,6 +9947,55 @@
         <v>0.77</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>48.567</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>78.625</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9847,7 +10007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11652,6 +11812,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3375,6 +3375,55 @@
         <v>0.96</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>49.233</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>80.125</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>4.211</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="O59" s="5" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3386,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5222,6 +5271,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5233,7 +5313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7069,6 +7149,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7080,7 +7191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9996,6 +10107,55 @@
         <v>0.96</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>49.233</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>80.125</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>4.211</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="O59" s="5" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10007,7 +10167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11843,6 +12003,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3424,6 +3424,55 @@
         <v>0.57</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>49.733</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3435,7 +3484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5302,6 +5351,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5313,7 +5393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7180,6 +7260,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7191,7 +7302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10156,6 +10267,55 @@
         <v>0.57</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>49.733</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10167,7 +10327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12034,6 +12194,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3473,6 +3473,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>49.667</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O61" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3484,7 +3533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5382,6 +5431,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5393,7 +5473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7291,6 +7371,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7302,7 +7413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10316,6 +10427,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>49.667</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O61" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10327,7 +10487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12225,6 +12385,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3522,6 +3522,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>49.667</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3533,7 +3582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5462,6 +5511,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5473,7 +5553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7402,6 +7482,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7413,7 +7524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10476,6 +10587,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>49.667</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10487,7 +10647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12416,6 +12576,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3571,6 +3571,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>49.767</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O63" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3582,7 +3631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5542,6 +5591,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5553,7 +5633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7513,6 +7593,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7524,7 +7635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10636,6 +10747,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>49.767</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O63" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10647,7 +10807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12607,6 +12767,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>15.438</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3620,6 +3620,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>49.833</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3631,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5622,6 +5671,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5633,7 +5713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7624,6 +7704,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7635,7 +7746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10796,6 +10907,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>49.833</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10807,7 +10967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12798,6 +12958,37 @@
         <v>4.79</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3669,6 +3669,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>50.233</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O65" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3680,7 +3729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5702,6 +5751,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5713,7 +5793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7735,6 +7815,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7746,7 +7857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10956,6 +11067,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>50.233</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O65" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10967,7 +11127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12989,6 +13149,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3718,6 +3718,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>50.333</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3729,7 +3778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5782,6 +5831,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5793,7 +5873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7846,6 +7926,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7857,7 +7968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11116,6 +11227,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>50.333</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11127,7 +11287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13180,6 +13340,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3767,6 +3767,55 @@
         <v>0.45</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>50.833</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>42.143</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="5" t="n">
+        <v>13.429</v>
+      </c>
+      <c r="O67" s="5" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3778,7 +3827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5862,6 +5911,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5873,7 +5953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7957,6 +8037,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7968,7 +8079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11276,6 +11387,55 @@
         <v>0.45</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>50.833</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>42.143</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="5" t="n">
+        <v>13.429</v>
+      </c>
+      <c r="O67" s="5" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11287,7 +11447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13371,6 +13531,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3816,6 +3816,55 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>50.833</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>42.143</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="5" t="n">
+        <v>13.429</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3827,7 +3876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5942,6 +5991,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5953,7 +6033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8068,6 +8148,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8079,7 +8190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11436,6 +11547,55 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>50.833</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>42.143</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="5" t="n">
+        <v>13.429</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11447,7 +11607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13562,6 +13722,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3865,6 +3865,55 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>50.833</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>42.143</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="5" t="n">
+        <v>13.429</v>
+      </c>
+      <c r="O69" s="5" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3876,7 +3925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6022,6 +6071,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6033,7 +6113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8179,6 +8259,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8190,7 +8301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11596,6 +11707,55 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>50.833</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>42.143</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>4.216</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="5" t="n">
+        <v>13.429</v>
+      </c>
+      <c r="O69" s="5" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11607,7 +11767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13753,6 +13913,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>31.391</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3914,6 +3914,55 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>50.833</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>42.143</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N70" s="5" t="n">
+        <v>13.595</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3925,7 +3974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6102,6 +6151,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6113,7 +6193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8290,6 +8370,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8301,7 +8412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11756,6 +11867,55 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>50.833</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>42.143</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N70" s="5" t="n">
+        <v>13.595</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11767,7 +11927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13944,6 +14104,37 @@
         <v>0.73</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3963,6 +3963,55 @@
         <v>1.24</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>50.933</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>42.077</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>4.212</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N71" s="5" t="n">
+        <v>13.714</v>
+      </c>
+      <c r="O71" s="5" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3974,7 +4023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6182,6 +6231,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6193,7 +6273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8401,6 +8481,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8412,7 +8523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11916,6 +12027,55 @@
         <v>1.24</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>50.933</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>42.077</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>4.212</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N71" s="5" t="n">
+        <v>13.714</v>
+      </c>
+      <c r="O71" s="5" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11927,7 +12087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14135,6 +14295,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4012,6 +4012,55 @@
         <v>0.88</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>50.933</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>84.732</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>42.077</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>4.212</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4023,7 +4072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6262,6 +6311,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6273,7 +6353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8512,6 +8592,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8523,7 +8634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12076,6 +12187,55 @@
         <v>0.88</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>50.933</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>84.732</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>42.077</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>4.212</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12087,7 +12247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14326,6 +14486,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4061,6 +4061,55 @@
         <v>0.52</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>50.933</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>84.976</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N73" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O73" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4072,7 +4121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6342,6 +6391,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6353,7 +6433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8623,6 +8703,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8634,7 +8745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12236,6 +12347,55 @@
         <v>0.52</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>50.933</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>84.976</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N73" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O73" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12247,7 +12407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14517,6 +14677,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4110,6 +4110,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>50.967</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>85.22</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4121,7 +4170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6422,6 +6471,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6433,7 +6513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8734,6 +8814,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8745,7 +8856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12396,6 +12507,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>50.967</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>85.22</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12407,7 +12567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14708,6 +14868,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4159,6 +4159,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>50.967</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>85.22</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O75" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4170,7 +4219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6502,6 +6551,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6513,7 +6593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8845,6 +8925,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8856,7 +8967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12556,6 +12667,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>50.967</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>85.22</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O75" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12567,7 +12727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14899,6 +15059,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4208,6 +4208,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>50.967</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>85.22</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O76" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4219,7 +4268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6582,6 +6631,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6593,7 +6673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8956,6 +9036,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8967,7 +9078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12716,6 +12827,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>50.967</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>85.22</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O76" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12727,7 +12887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15090,6 +15250,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>32.565</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4257,6 +4257,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>85.70699999999999</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="5" t="n">
+        <v>13.838</v>
+      </c>
+      <c r="O77" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4268,7 +4317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6662,6 +6711,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6673,7 +6753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9067,6 +9147,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9078,7 +9189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12876,6 +12987,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>85.70699999999999</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="5" t="n">
+        <v>13.838</v>
+      </c>
+      <c r="O77" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12887,7 +13047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15281,6 +15441,37 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4306,6 +4306,55 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>51.333</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>85.95099999999999</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>13.852</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4317,7 +4366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6742,6 +6791,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6753,7 +6833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9178,6 +9258,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9189,7 +9300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13036,6 +13147,55 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>51.333</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>85.95099999999999</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>13.852</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13047,7 +13207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15472,6 +15632,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4355,6 +4355,55 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>51.333</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>86.19499999999999</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="5" t="n">
+        <v>13.919</v>
+      </c>
+      <c r="O79" s="5" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4366,7 +4415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6822,6 +6871,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6833,7 +6913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9289,6 +9369,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9300,7 +9411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13196,6 +13307,55 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>51.333</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>86.19499999999999</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>42.112</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="5" t="n">
+        <v>13.919</v>
+      </c>
+      <c r="O79" s="5" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13207,7 +13367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15663,6 +15823,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4404,6 +4404,55 @@
         <v>0.38</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>51.333</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>86.68300000000001</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>42.237</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="5" t="n">
+        <v>13.948</v>
+      </c>
+      <c r="O80" s="5" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4415,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6902,6 +6951,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6913,7 +6993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9400,6 +9480,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9411,7 +9522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13356,6 +13467,55 @@
         <v>0.38</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>51.333</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>86.68300000000001</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>42.237</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="5" t="n">
+        <v>13.948</v>
+      </c>
+      <c r="O80" s="5" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13367,7 +13527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15854,6 +16014,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4453,6 +4453,55 @@
         <v>0.21</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>86.268</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="5" t="n">
+        <v>13.976</v>
+      </c>
+      <c r="O81" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4464,7 +4513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6982,6 +7031,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6993,7 +7073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9511,6 +9591,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9522,7 +9633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13516,6 +13627,55 @@
         <v>0.21</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>86.268</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="5" t="n">
+        <v>13.976</v>
+      </c>
+      <c r="O81" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13527,7 +13687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16045,6 +16205,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4502,6 +4502,55 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>86.268</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="5" t="n">
+        <v>13.976</v>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4513,7 +4562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7062,6 +7111,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7073,7 +7153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9622,6 +9702,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9633,7 +9744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13676,6 +13787,55 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>86.268</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="5" t="n">
+        <v>13.976</v>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13687,7 +13847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16236,6 +16396,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4551,6 +4551,55 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>86.268</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="5" t="n">
+        <v>13.976</v>
+      </c>
+      <c r="O83" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4562,7 +4611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7142,6 +7191,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7153,7 +7233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9733,6 +9813,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9744,7 +9855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13836,6 +13947,55 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>86.268</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="5" t="n">
+        <v>13.976</v>
+      </c>
+      <c r="O83" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13847,7 +14007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16427,6 +16587,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4600,6 +4600,55 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>51.767</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="5" t="n">
+        <v>14.024</v>
+      </c>
+      <c r="O84" s="5" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4611,7 +4660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7222,6 +7271,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7233,7 +7313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9844,6 +9924,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9855,7 +9966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13996,6 +14107,55 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>51.767</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="5" t="n">
+        <v>14.024</v>
+      </c>
+      <c r="O84" s="5" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14007,7 +14167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16618,6 +16778,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>32.913</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4649,6 +4649,55 @@
         <v>0.34</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>51.933</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>86.866</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>11.375</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>42.504</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>4.206</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N85" s="5" t="n">
+        <v>14.024</v>
+      </c>
+      <c r="O85" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4660,7 +4709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7302,6 +7351,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7313,7 +7393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9955,6 +10035,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9966,7 +10077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14156,6 +14267,55 @@
         <v>0.34</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>51.933</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>86.866</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>11.375</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>42.504</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>4.206</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N85" s="5" t="n">
+        <v>14.024</v>
+      </c>
+      <c r="O85" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14167,7 +14327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16809,6 +16969,37 @@
         <v>1.02</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4698,6 +4698,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>52.333</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>87.354</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N86" s="5" t="n">
+        <v>14.007</v>
+      </c>
+      <c r="O86" s="5" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4709,7 +4758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7382,6 +7431,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7393,7 +7473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10066,6 +10146,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10077,7 +10188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14316,6 +14427,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>52.333</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>87.354</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N86" s="5" t="n">
+        <v>14.007</v>
+      </c>
+      <c r="O86" s="5" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14327,7 +14487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17000,6 +17160,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4747,6 +4747,55 @@
         <v>-0.12</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>87.72</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="5" t="n">
+        <v>13.978</v>
+      </c>
+      <c r="O87" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4758,7 +4807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7462,6 +7511,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7473,7 +7553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10177,6 +10257,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10188,7 +10299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14476,6 +14587,55 @@
         <v>-0.12</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>87.72</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="5" t="n">
+        <v>13.978</v>
+      </c>
+      <c r="O87" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14487,7 +14647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17191,6 +17351,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4796,6 +4796,55 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>88.20699999999999</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>42.717</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N88" s="5" t="n">
+        <v>13.978</v>
+      </c>
+      <c r="O88" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4807,7 +4856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7542,6 +7591,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7553,7 +7633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10288,6 +10368,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10299,7 +10410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14636,6 +14747,55 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>88.20699999999999</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>42.717</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N88" s="5" t="n">
+        <v>13.978</v>
+      </c>
+      <c r="O88" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14647,7 +14807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17382,6 +17542,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4845,6 +4845,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>52.733</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>88.20699999999999</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>42.717</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N89" s="5" t="n">
+        <v>13.978</v>
+      </c>
+      <c r="O89" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4856,7 +4905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7622,6 +7671,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7633,7 +7713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10399,6 +10479,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10410,7 +10521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14796,6 +14907,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>52.733</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>88.20699999999999</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>42.717</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N89" s="5" t="n">
+        <v>13.978</v>
+      </c>
+      <c r="O89" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14807,7 +14967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17573,6 +17733,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4894,6 +4894,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>52.733</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>88.20699999999999</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>42.717</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N90" s="5" t="n">
+        <v>13.978</v>
+      </c>
+      <c r="O90" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4905,7 +4954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7702,6 +7751,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7713,7 +7793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10510,6 +10590,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10521,7 +10632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14956,6 +15067,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>52.733</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>88.20699999999999</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>42.717</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N90" s="5" t="n">
+        <v>13.978</v>
+      </c>
+      <c r="O90" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14967,7 +15127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17764,6 +17924,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4943,6 +4943,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>52.733</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>88.69499999999999</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>42.895</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>4.229</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N91" s="5" t="n">
+        <v>13.982</v>
+      </c>
+      <c r="O91" s="5" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4954,7 +5003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7782,6 +7831,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7793,7 +7873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10621,6 +10701,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10632,7 +10743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15116,6 +15227,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>52.733</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>88.69499999999999</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>42.895</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>4.229</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N91" s="5" t="n">
+        <v>13.982</v>
+      </c>
+      <c r="O91" s="5" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15127,7 +15287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17955,6 +18115,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4992,6 +4992,55 @@
         <v>0.03</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>52.733</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>89.42700000000001</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>42.895</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>4.236</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N92" s="5" t="n">
+        <v>13.982</v>
+      </c>
+      <c r="O92" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5003,7 +5052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7862,6 +7911,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7873,7 +7953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10732,6 +10812,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10743,7 +10854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15276,6 +15387,55 @@
         <v>0.03</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>52.733</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>89.42700000000001</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>42.895</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>4.236</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N92" s="5" t="n">
+        <v>13.982</v>
+      </c>
+      <c r="O92" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15287,7 +15447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18146,6 +18306,37 @@
         <v>5.21</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5041,6 +5041,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>53.167</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>90.098</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>11.275</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>42.895</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>4.236</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="5" t="n">
+        <v>13.961</v>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5052,7 +5101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7942,6 +7991,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7953,7 +8033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10843,6 +10923,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10854,7 +10965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15436,6 +15547,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>53.167</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>90.098</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>11.275</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>42.895</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>4.236</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="5" t="n">
+        <v>13.961</v>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15447,7 +15607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18337,6 +18497,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5090,6 +5090,55 @@
         <v>-0.21</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>53.433</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>90.098</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>11.275</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>43.138</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>4.239</v>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N94" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O94" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5101,7 +5150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8022,6 +8071,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8033,7 +8113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10954,6 +11034,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10965,7 +11076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15596,6 +15707,55 @@
         <v>-0.21</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>53.433</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>90.098</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>11.275</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>43.138</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>4.239</v>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N94" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O94" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15607,7 +15767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18528,6 +18688,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5139,6 +5139,55 @@
         <v>-0.1</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>91.07299999999999</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>43.288</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>4.239</v>
+      </c>
+      <c r="M95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O95" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5150,7 +5199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8102,6 +8151,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8113,7 +8193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11065,6 +11145,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11076,7 +11187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15756,6 +15867,55 @@
         <v>-0.1</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>91.07299999999999</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>43.288</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>4.239</v>
+      </c>
+      <c r="M95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O95" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15767,7 +15927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18719,6 +18879,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5188,6 +5188,55 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>91.07299999999999</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>43.288</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>4.246</v>
+      </c>
+      <c r="M96" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N96" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O96" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5199,7 +5248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8182,6 +8231,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8193,7 +8273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11176,6 +11256,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11187,7 +11298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15916,6 +16027,55 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>91.07299999999999</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>43.288</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>4.246</v>
+      </c>
+      <c r="M96" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N96" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O96" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15927,7 +16087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18910,6 +19070,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5237,6 +5237,55 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>91.07299999999999</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>43.288</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>4.246</v>
+      </c>
+      <c r="M97" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N97" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O97" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5248,7 +5297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8262,6 +8311,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8273,7 +8353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11287,6 +11367,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11298,7 +11409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16076,6 +16187,55 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>91.07299999999999</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>11.325</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>43.288</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>4.246</v>
+      </c>
+      <c r="M97" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N97" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O97" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16087,7 +16247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19101,6 +19261,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5286,6 +5286,55 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>91.31699999999999</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>43.288</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>4.246</v>
+      </c>
+      <c r="M98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O98" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5297,7 +5346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8342,6 +8391,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8353,7 +8433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11398,6 +11478,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11409,7 +11520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16236,6 +16347,55 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>91.31699999999999</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>43.288</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>4.246</v>
+      </c>
+      <c r="M98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O98" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16247,7 +16407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19292,6 +19452,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O98"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5335,6 +5335,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>54.167</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>90.56100000000001</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>43.377</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>4.262</v>
+      </c>
+      <c r="M99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O99" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5346,7 +5395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8422,6 +8471,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8433,7 +8513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11509,6 +11589,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11520,7 +11631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O98"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16396,6 +16507,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>54.167</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>90.56100000000001</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>43.377</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>4.262</v>
+      </c>
+      <c r="M99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O99" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16407,7 +16567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19483,6 +19643,37 @@
         <v>2.95</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5384,6 +5384,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>54.167</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>90.80500000000001</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>11.375</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>43.637</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>4.266</v>
+      </c>
+      <c r="M100" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N100" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O100" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5395,7 +5444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8502,6 +8551,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8513,7 +8593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11620,6 +11700,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11631,7 +11742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16556,6 +16667,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>54.167</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>90.80500000000001</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>11.375</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>43.637</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>4.266</v>
+      </c>
+      <c r="M100" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N100" s="5" t="n">
+        <v>13.947</v>
+      </c>
+      <c r="O100" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16567,7 +16727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19674,6 +19834,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5433,6 +5433,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>53.933</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>91.04900000000001</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>11.425</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>44.011</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>4.362</v>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N101" s="5" t="n">
+        <v>13.932</v>
+      </c>
+      <c r="O101" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5444,7 +5493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8582,6 +8631,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8593,7 +8673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11731,6 +11811,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11742,7 +11853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16716,6 +16827,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>53.933</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>91.04900000000001</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>11.425</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>44.011</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>4.362</v>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N101" s="5" t="n">
+        <v>13.932</v>
+      </c>
+      <c r="O101" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16727,7 +16887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19865,6 +20025,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5482,6 +5482,55 @@
         <v>-0.11</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>53.933</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>91.29300000000001</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>11.475</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>44.189</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>4.443</v>
+      </c>
+      <c r="M102" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N102" s="5" t="n">
+        <v>13.883</v>
+      </c>
+      <c r="O102" s="5" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5493,7 +5542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8662,6 +8711,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8673,7 +8753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11842,6 +11922,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11853,7 +11964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16876,6 +16987,55 @@
         <v>-0.11</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>53.933</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>91.29300000000001</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>11.475</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>44.189</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>4.443</v>
+      </c>
+      <c r="M102" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N102" s="5" t="n">
+        <v>13.883</v>
+      </c>
+      <c r="O102" s="5" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16887,7 +17047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20056,6 +20216,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5531,6 +5531,55 @@
         <v>-0.35</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>53.933</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>91.29300000000001</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>11.475</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>44.189</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>4.443</v>
+      </c>
+      <c r="M103" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N103" s="5" t="n">
+        <v>13.883</v>
+      </c>
+      <c r="O103" s="5" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5542,7 +5591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8742,6 +8791,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8753,7 +8833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11953,6 +12033,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11964,7 +12075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17036,6 +17147,55 @@
         <v>-0.35</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>53.933</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>91.29300000000001</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>11.475</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>44.189</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>4.443</v>
+      </c>
+      <c r="M103" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N103" s="5" t="n">
+        <v>13.883</v>
+      </c>
+      <c r="O103" s="5" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17047,7 +17207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20247,6 +20407,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5580,6 +5580,55 @@
         <v>-0.35</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>53.933</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>91.29300000000001</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>11.475</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>44.189</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>4.443</v>
+      </c>
+      <c r="M104" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N104" s="5" t="n">
+        <v>13.883</v>
+      </c>
+      <c r="O104" s="5" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5591,7 +5640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8822,6 +8871,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8833,7 +8913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12064,6 +12144,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12075,7 +12186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17196,6 +17307,55 @@
         <v>-0.35</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>53.933</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>91.29300000000001</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>11.475</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>44.189</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>4.443</v>
+      </c>
+      <c r="M104" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N104" s="5" t="n">
+        <v>13.883</v>
+      </c>
+      <c r="O104" s="5" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17207,7 +17367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20438,6 +20598,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>36.587</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5629,6 +5629,55 @@
         <v>-0.35</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>53.917</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>44.367</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M105" s="5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N105" s="5" t="n">
+        <v>13.854</v>
+      </c>
+      <c r="O105" s="5" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5640,7 +5689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8902,6 +8951,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8913,7 +8993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12175,6 +12255,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12186,7 +12297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17356,6 +17467,55 @@
         <v>-0.35</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>53.917</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>11.525</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>44.367</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M105" s="5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N105" s="5" t="n">
+        <v>13.854</v>
+      </c>
+      <c r="O105" s="5" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17367,7 +17527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20629,6 +20789,37 @@
         <v>2.87</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5678,6 +5678,55 @@
         <v>-0.21</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>54.083</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>92.024</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>11.575</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>44.544</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="M106" s="5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N106" s="5" t="n">
+        <v>13.854</v>
+      </c>
+      <c r="O106" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5689,7 +5738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8982,6 +9031,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8993,7 +9073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12286,6 +12366,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12297,7 +12408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17516,6 +17627,55 @@
         <v>-0.21</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>54.083</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>92.024</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>11.575</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>44.544</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="M106" s="5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N106" s="5" t="n">
+        <v>13.854</v>
+      </c>
+      <c r="O106" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17527,7 +17687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20820,6 +20980,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O106"/>
+  <dimension ref="A1:O107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5727,6 +5727,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>92.649</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>44.571</v>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="M107" s="5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N107" s="5" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="O107" s="5" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5738,7 +5787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9062,6 +9111,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9073,7 +9153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12397,6 +12477,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12408,7 +12519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O106"/>
+  <dimension ref="A1:O107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17676,6 +17787,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>92.649</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>44.571</v>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="M107" s="5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N107" s="5" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="O107" s="5" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17687,7 +17847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21011,6 +21171,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -5764,10 +5764,10 @@
         <v>0.06</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="N107" s="5" t="n">
         <v>13.83</v>
@@ -17824,10 +17824,10 @@
         <v>0.06</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="N107" s="5" t="n">
         <v>13.83</v>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O107"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5776,6 +5776,55 @@
         <v>-0.17</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>92.91200000000001</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>11.775</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>44.571</v>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="M108" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N108" s="5" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="O108" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5787,7 +5836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9142,6 +9191,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9153,7 +9233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12508,6 +12588,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12519,7 +12630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O107"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17836,6 +17947,55 @@
         <v>-0.17</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>92.91200000000001</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>11.775</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>44.571</v>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="M108" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N108" s="5" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="O108" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17847,7 +18007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21202,6 +21362,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5825,6 +5825,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>54.067</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="M109" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N109" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O109" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5836,7 +5885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9222,6 +9271,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9233,7 +9313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12619,6 +12699,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12630,7 +12741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17996,6 +18107,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>54.067</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="M109" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N109" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O109" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18007,7 +18167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21393,6 +21553,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>37.587</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>18.438</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5874,6 +5874,55 @@
         <v>-0.15</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>54.133</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>45.357</v>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="M110" s="5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N110" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O110" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5885,7 +5934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9302,6 +9351,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9313,7 +9393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12730,6 +12810,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12741,7 +12852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18156,6 +18267,55 @@
         <v>-0.15</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>54.133</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>11.975</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>45.357</v>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="M110" s="5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N110" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O110" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18167,7 +18327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21584,6 +21744,37 @@
         <v>2.79</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5923,6 +5923,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>12.088</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>45.364</v>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="M111" s="5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N111" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O111" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5934,7 +5983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9382,6 +9431,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9393,7 +9473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12841,6 +12921,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12852,7 +12963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18316,6 +18427,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>12.088</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>45.364</v>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="M111" s="5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N111" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O111" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18327,7 +18487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21775,6 +21935,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5972,6 +5972,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>12.213</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>45.321</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="M112" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N112" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O112" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5983,7 +6032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9462,6 +9511,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9473,7 +9553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12952,6 +13032,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12963,7 +13074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18476,6 +18587,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>12.213</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>45.321</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="M112" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N112" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O112" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18487,7 +18647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21966,6 +22126,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O112"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6021,6 +6021,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>45.279</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M113" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N113" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O113" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6032,7 +6081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9542,6 +9591,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9553,7 +9633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13063,6 +13143,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13074,7 +13185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O112"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18636,6 +18747,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>45.279</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M113" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N113" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O113" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18647,7 +18807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22157,6 +22317,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6070,6 +6070,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>45.214</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="M114" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N114" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O114" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6081,7 +6130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9622,6 +9671,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9633,7 +9713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13174,6 +13254,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13185,7 +13296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18796,6 +18907,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>45.214</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="M114" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N114" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O114" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18807,7 +18967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22348,6 +22508,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>38.587</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
